--- a/checkrates/week-19/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-19/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -847,14 +847,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>B2C · BKGS&gt;0 · peor Eficacia · ordenado ↑</t>
+          <t>B2C · BKGS&gt;0 · peor Eficacia · ordenado por Eficacia ↑ (menor primero)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6314,18 +6314,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6345,7 +6346,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6362,35 +6363,40 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>CR_Unicos</t>
         </is>
       </c>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>Successful</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>Bookings</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>Eficacia</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="H5" s="3" t="inlineStr">
         <is>
           <t>ConvRate</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="I5" s="3" t="inlineStr">
         <is>
           <t>BandaEficacia</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>BandaConvRate</t>
         </is>
@@ -6405,27 +6411,32 @@
           <t>Hilton</t>
         </is>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, HBSI, Internal</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
         <v>73567</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="E6" s="12" t="n">
         <v>66833</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="F6" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.9084643930022972</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.0003126401783408322</v>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6440,27 +6451,32 @@
           <t>Hyatt</t>
         </is>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
         <v>48369</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="E7" s="12" t="n">
         <v>46030</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="F7" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="G7" s="13" t="n">
         <v>0.9516425809919576</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.001426533523537803</v>
       </c>
-      <c r="H7" s="9" t="inlineStr">
+      <c r="I7" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6475,27 +6491,32 @@
           <t>IHG</t>
         </is>
       </c>
-      <c r="C8" s="12" t="n">
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
         <v>43028</v>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="E8" s="12" t="n">
         <v>42216</v>
       </c>
-      <c r="E8" s="12" t="n">
+      <c r="F8" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="G8" s="13" t="n">
         <v>0.9811285674444548</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.000209166124384122</v>
       </c>
-      <c r="H8" s="10" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6510,27 +6531,32 @@
           <t>AA-Independent</t>
         </is>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, HBSI, Internal, Siteminder, SynXis, Travelclick</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
         <v>20615</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="E9" s="12" t="n">
         <v>19290</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="F9" s="12" t="n">
         <v>428</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="G9" s="13" t="n">
         <v>0.9357264128062091</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.02076158137278681</v>
       </c>
-      <c r="H9" s="9" t="inlineStr">
+      <c r="I9" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -6545,27 +6571,32 @@
           <t>Accor</t>
         </is>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, Internal</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>12861</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="E10" s="12" t="n">
         <v>12217</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="F10" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.9499261332711297</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.001321825674519866</v>
       </c>
-      <c r="H10" s="9" t="inlineStr">
+      <c r="I10" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6580,27 +6611,32 @@
           <t>Wyndham</t>
         </is>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>11295</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="E11" s="12" t="n">
         <v>10547</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.93377600708278</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="H11" s="13" t="n">
         <v>0.001505090748118637</v>
       </c>
-      <c r="H11" s="9" t="inlineStr">
+      <c r="I11" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6615,27 +6651,32 @@
           <t>Caesars Entertainment</t>
         </is>
       </c>
-      <c r="C12" s="12" t="n">
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>8394</v>
       </c>
-      <c r="D12" s="12" t="n">
+      <c r="E12" s="12" t="n">
         <v>6296</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F12" s="13" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.7500595663569216</v>
       </c>
-      <c r="G12" s="13" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.002859185132237312</v>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6650,27 +6691,32 @@
           <t>Hyatt Inclusive Collection</t>
         </is>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>4162</v>
       </c>
-      <c r="D13" s="12" t="n">
+      <c r="E13" s="12" t="n">
         <v>4156</v>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F13" s="13" t="n">
+      <c r="G13" s="13" t="n">
         <v>0.9985583853916387</v>
       </c>
-      <c r="G13" s="13" t="n">
+      <c r="H13" s="13" t="n">
         <v>0.003844305622296973</v>
       </c>
-      <c r="H13" s="10" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6685,27 +6731,32 @@
           <t>Disney</t>
         </is>
       </c>
-      <c r="C14" s="12" t="n">
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>3453</v>
       </c>
-      <c r="D14" s="12" t="n">
+      <c r="E14" s="12" t="n">
         <v>3416</v>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="G14" s="13" t="n">
         <v>0.9892846799884158</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="H14" s="13" t="n">
         <v>0.01013611352447147</v>
       </c>
-      <c r="H14" s="10" t="inlineStr">
+      <c r="I14" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6720,27 +6771,32 @@
           <t>MGM Resorts</t>
         </is>
       </c>
-      <c r="C15" s="12" t="n">
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="n">
         <v>3051</v>
       </c>
-      <c r="D15" s="12" t="n">
+      <c r="E15" s="12" t="n">
         <v>2962</v>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="G15" s="13" t="n">
         <v>0.970829236315962</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="H15" s="13" t="n">
         <v>0.0006555227794165847</v>
       </c>
-      <c r="H15" s="10" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6755,27 +6811,32 @@
           <t>Best Western</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n">
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, SynXis</t>
+        </is>
+      </c>
+      <c r="D16" s="12" t="n">
         <v>2890</v>
       </c>
-      <c r="D16" s="12" t="n">
+      <c r="E16" s="12" t="n">
         <v>2811</v>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="G16" s="13" t="n">
         <v>0.9726643598615917</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="H16" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H16" s="10" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -6790,27 +6851,32 @@
           <t>Universal</t>
         </is>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>2117</v>
       </c>
-      <c r="D17" s="12" t="n">
+      <c r="E17" s="12" t="n">
         <v>1681</v>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="G17" s="13" t="n">
         <v>0.7940481813887577</v>
       </c>
-      <c r="G17" s="13" t="n">
+      <c r="H17" s="13" t="n">
         <v>0.005668398677373642</v>
       </c>
-      <c r="H17" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6825,27 +6891,32 @@
           <t>CHOICE</t>
         </is>
       </c>
-      <c r="C18" s="12" t="n">
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Expedia, Internal</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="n">
         <v>1676</v>
       </c>
-      <c r="D18" s="12" t="n">
+      <c r="E18" s="12" t="n">
         <v>1616</v>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="F18" s="13" t="n">
+      <c r="G18" s="13" t="n">
         <v>0.964200477326969</v>
       </c>
-      <c r="G18" s="13" t="n">
+      <c r="H18" s="13" t="n">
         <v>0.01312649164677804</v>
       </c>
-      <c r="H18" s="9" t="inlineStr">
+      <c r="I18" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -6860,27 +6931,32 @@
           <t>Barcelo</t>
         </is>
       </c>
-      <c r="C19" s="12" t="n">
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="n">
         <v>1608</v>
       </c>
-      <c r="D19" s="12" t="n">
+      <c r="E19" s="12" t="n">
         <v>1531</v>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="G19" s="13" t="n">
         <v>0.9521144278606966</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="H19" s="13" t="n">
         <v>0.001865671641791045</v>
       </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="I19" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6895,27 +6971,32 @@
           <t>PAM Hotels</t>
         </is>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Internal, SynXis</t>
+        </is>
+      </c>
+      <c r="D20" s="12" t="n">
         <v>1017</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="E20" s="12" t="n">
         <v>1005</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="G20" s="13" t="n">
         <v>0.9882005899705014</v>
       </c>
-      <c r="G20" s="13" t="n">
+      <c r="H20" s="13" t="n">
         <v>0.005899705014749262</v>
       </c>
-      <c r="H20" s="10" t="inlineStr">
+      <c r="I20" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -6930,27 +7011,32 @@
           <t>Camino Real</t>
         </is>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Travelclick</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>975</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="E21" s="12" t="n">
         <v>974</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="G21" s="13" t="n">
         <v>0.9989743589743589</v>
       </c>
-      <c r="G21" s="13" t="n">
+      <c r="H21" s="13" t="n">
         <v>0.06974358974358974</v>
       </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -6965,27 +7051,32 @@
           <t>Presidente Intercontinental</t>
         </is>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>DerbySoft, Internal</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>841</v>
       </c>
-      <c r="D22" s="12" t="n">
+      <c r="E22" s="12" t="n">
         <v>713</v>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="G22" s="13" t="n">
         <v>0.8478002378121284</v>
       </c>
-      <c r="G22" s="13" t="n">
+      <c r="H22" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7000,27 +7091,32 @@
           <t>Wynn Las Vegas</t>
         </is>
       </c>
-      <c r="C23" s="12" t="n">
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D23" s="12" t="n">
         <v>753</v>
       </c>
-      <c r="D23" s="12" t="n">
+      <c r="E23" s="12" t="n">
         <v>751</v>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F23" s="13" t="n">
+      <c r="G23" s="13" t="n">
         <v>0.9973439575033201</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="H23" s="13" t="n">
         <v>0.006640106241699867</v>
       </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="I23" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7035,27 +7131,32 @@
           <t>GRUPO POSADAS</t>
         </is>
       </c>
-      <c r="C24" s="12" t="n">
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>747</v>
       </c>
-      <c r="D24" s="12" t="n">
+      <c r="E24" s="12" t="n">
         <v>722</v>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="G24" s="13" t="n">
         <v>0.9665327978580991</v>
       </c>
-      <c r="G24" s="13" t="n">
+      <c r="H24" s="13" t="n">
         <v>0.008032128514056224</v>
       </c>
-      <c r="H24" s="9" t="inlineStr">
+      <c r="I24" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7070,27 +7171,32 @@
           <t>Hoteles Geh Suites</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="n">
         <v>743</v>
       </c>
-      <c r="D25" s="12" t="n">
+      <c r="E25" s="12" t="n">
         <v>720</v>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="G25" s="13" t="n">
         <v>0.9690444145356663</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="H25" s="13" t="n">
         <v>0.0107671601615074</v>
       </c>
-      <c r="H25" s="9" t="inlineStr">
+      <c r="I25" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7105,27 +7211,32 @@
           <t>Decameron</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="n">
         <v>693</v>
       </c>
-      <c r="D26" s="12" t="n">
+      <c r="E26" s="12" t="n">
         <v>598</v>
       </c>
-      <c r="E26" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G26" s="13" t="n">
         <v>0.862914862914863</v>
       </c>
-      <c r="G26" s="13" t="n">
+      <c r="H26" s="13" t="n">
         <v>0.001443001443001443</v>
       </c>
-      <c r="H26" s="8" t="inlineStr">
+      <c r="I26" s="8" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7140,27 +7251,32 @@
           <t>Oasis</t>
         </is>
       </c>
-      <c r="C27" s="12" t="n">
-        <v>551</v>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D27" s="12" t="n">
         <v>551</v>
       </c>
       <c r="E27" s="12" t="n">
+        <v>551</v>
+      </c>
+      <c r="F27" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F27" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G27" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="13" t="n">
         <v>0.003629764065335753</v>
       </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="I27" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7175,27 +7291,32 @@
           <t>Americas Hotels Group</t>
         </is>
       </c>
-      <c r="C28" s="12" t="n">
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="n">
         <v>481</v>
       </c>
-      <c r="D28" s="12" t="n">
+      <c r="E28" s="12" t="n">
         <v>465</v>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F28" s="13" t="n">
+      <c r="G28" s="13" t="n">
         <v>0.9667359667359667</v>
       </c>
-      <c r="G28" s="13" t="n">
+      <c r="H28" s="13" t="n">
         <v>0.03534303534303534</v>
       </c>
-      <c r="H28" s="9" t="inlineStr">
+      <c r="I28" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -7210,27 +7331,32 @@
           <t>Emporio</t>
         </is>
       </c>
-      <c r="C29" s="12" t="n">
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="n">
         <v>478</v>
       </c>
-      <c r="D29" s="12" t="n">
+      <c r="E29" s="12" t="n">
         <v>476</v>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="G29" s="13" t="n">
         <v>0.99581589958159</v>
       </c>
-      <c r="G29" s="13" t="n">
+      <c r="H29" s="13" t="n">
         <v>0.006276150627615063</v>
       </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="I29" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7245,27 +7371,32 @@
           <t>Marriott</t>
         </is>
       </c>
-      <c r="C30" s="12" t="n">
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Omnibees</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="n">
         <v>475</v>
       </c>
-      <c r="D30" s="12" t="n">
+      <c r="E30" s="12" t="n">
         <v>468</v>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="G30" s="13" t="n">
         <v>0.9852631578947368</v>
       </c>
-      <c r="G30" s="13" t="n">
+      <c r="H30" s="13" t="n">
         <v>0.008421052631578947</v>
       </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="I30" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7280,27 +7411,32 @@
           <t>Mision</t>
         </is>
       </c>
-      <c r="C31" s="12" t="n">
-        <v>450</v>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D31" s="12" t="n">
         <v>450</v>
       </c>
       <c r="E31" s="12" t="n">
+        <v>450</v>
+      </c>
+      <c r="F31" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G31" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="13" t="n">
         <v>0.04666666666666667</v>
       </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -7315,27 +7451,32 @@
           <t>Park Royal</t>
         </is>
       </c>
-      <c r="C32" s="12" t="n">
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D32" s="12" t="n">
         <v>431</v>
       </c>
-      <c r="D32" s="12" t="n">
+      <c r="E32" s="12" t="n">
         <v>422</v>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="G32" s="13" t="n">
         <v>0.9791183294663574</v>
       </c>
-      <c r="G32" s="13" t="n">
+      <c r="H32" s="13" t="n">
         <v>0.004640371229698376</v>
       </c>
-      <c r="H32" s="10" t="inlineStr">
+      <c r="I32" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7350,27 +7491,32 @@
           <t>Dann</t>
         </is>
       </c>
-      <c r="C33" s="12" t="n">
-        <v>410</v>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D33" s="12" t="n">
         <v>410</v>
       </c>
       <c r="E33" s="12" t="n">
+        <v>410</v>
+      </c>
+      <c r="F33" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G33" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="I33" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7385,27 +7531,32 @@
           <t>Hoteles Movich</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n">
-        <v>408</v>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D34" s="12" t="n">
         <v>408</v>
       </c>
       <c r="E34" s="12" t="n">
+        <v>408</v>
+      </c>
+      <c r="F34" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F34" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G34" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="13" t="n">
         <v>0.04166666666666666</v>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="I34" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -7420,27 +7571,32 @@
           <t>Iberostar</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>HBSI, Internal</t>
+        </is>
+      </c>
+      <c r="D35" s="12" t="n">
         <v>345</v>
       </c>
-      <c r="D35" s="12" t="n">
+      <c r="E35" s="12" t="n">
         <v>224</v>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="F35" s="13" t="n">
+      <c r="G35" s="13" t="n">
         <v>0.6492753623188405</v>
       </c>
-      <c r="G35" s="13" t="n">
+      <c r="H35" s="13" t="n">
         <v>0.03188405797101449</v>
       </c>
-      <c r="H35" s="7" t="inlineStr">
-        <is>
-          <t>Crítica</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
+        <is>
+          <t>Crítica</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -7455,27 +7611,32 @@
           <t>EM Hotels</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
-        <v>318</v>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D36" s="12" t="n">
         <v>318</v>
       </c>
       <c r="E36" s="12" t="n">
+        <v>318</v>
+      </c>
+      <c r="F36" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G36" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="I36" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7490,27 +7651,32 @@
           <t>Hoteles Xcaret</t>
         </is>
       </c>
-      <c r="C37" s="12" t="n">
-        <v>314</v>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D37" s="12" t="n">
         <v>314</v>
       </c>
       <c r="E37" s="12" t="n">
+        <v>314</v>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G37" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H37" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="I37" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7525,27 +7691,32 @@
           <t>Melia</t>
         </is>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>HBSI</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>311</v>
-      </c>
-      <c r="D38" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="13" t="n">
+      <c r="F38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G38" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H38" s="4" t="inlineStr">
+      <c r="H38" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7560,27 +7731,32 @@
           <t>Karisma</t>
         </is>
       </c>
-      <c r="C39" s="12" t="n">
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>SynXis</t>
+        </is>
+      </c>
+      <c r="D39" s="12" t="n">
         <v>305</v>
       </c>
-      <c r="D39" s="12" t="n">
+      <c r="E39" s="12" t="n">
         <v>287</v>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F39" s="13" t="n">
+      <c r="G39" s="13" t="n">
         <v>0.940983606557377</v>
       </c>
-      <c r="G39" s="13" t="n">
+      <c r="H39" s="13" t="n">
         <v>0.006557377049180328</v>
       </c>
-      <c r="H39" s="9" t="inlineStr">
+      <c r="I39" s="9" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7595,27 +7771,32 @@
           <t>Ocean by H10</t>
         </is>
       </c>
-      <c r="C40" s="12" t="n">
-        <v>277</v>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D40" s="12" t="n">
         <v>277</v>
       </c>
       <c r="E40" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F40" s="13" t="n">
+        <v>277</v>
+      </c>
+      <c r="F40" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G40" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="13" t="n">
         <v>0.003610108303249098</v>
       </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="I40" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7630,27 +7811,32 @@
           <t>Sandos</t>
         </is>
       </c>
-      <c r="C41" s="12" t="n">
-        <v>273</v>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D41" s="12" t="n">
         <v>273</v>
       </c>
       <c r="E41" s="12" t="n">
+        <v>273</v>
+      </c>
+      <c r="F41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G41" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="I41" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7665,27 +7851,32 @@
           <t>Palladium Hotel Group</t>
         </is>
       </c>
-      <c r="C42" s="12" t="n">
-        <v>257</v>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D42" s="12" t="n">
         <v>257</v>
       </c>
       <c r="E42" s="12" t="n">
+        <v>257</v>
+      </c>
+      <c r="F42" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F42" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G42" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="13" t="n">
         <v>0.03891050583657588</v>
       </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I42" s="5" t="inlineStr">
+      <c r="J42" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -7700,27 +7891,32 @@
           <t>Bahia Principe</t>
         </is>
       </c>
-      <c r="C43" s="12" t="n">
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D43" s="12" t="n">
         <v>241</v>
       </c>
-      <c r="D43" s="12" t="n">
+      <c r="E43" s="12" t="n">
         <v>239</v>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="13" t="n">
+      <c r="G43" s="13" t="n">
         <v>0.991701244813278</v>
       </c>
-      <c r="G43" s="13" t="n">
+      <c r="H43" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="I43" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I43" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7735,27 +7931,32 @@
           <t>GHL</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n">
-        <v>241</v>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D44" s="12" t="n">
         <v>241</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="13" t="n">
+        <v>241</v>
+      </c>
+      <c r="F44" s="12" t="n">
         <v>1</v>
       </c>
       <c r="G44" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="13" t="n">
         <v>0.004149377593360996</v>
       </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="I44" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I44" s="5" t="inlineStr">
+      <c r="J44" s="5" t="inlineStr">
         <is>
           <t>Crítica</t>
         </is>
@@ -7770,27 +7971,32 @@
           <t>Oxo Hotel</t>
         </is>
       </c>
-      <c r="C45" s="12" t="n">
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="n">
         <v>241</v>
       </c>
-      <c r="D45" s="12" t="n">
+      <c r="E45" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="F45" s="13" t="n">
+      <c r="G45" s="13" t="n">
         <v>0.995850622406639</v>
       </c>
-      <c r="G45" s="13" t="n">
+      <c r="H45" s="13" t="n">
         <v>0.02489626556016597</v>
       </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="I45" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I45" s="5" t="inlineStr">
+      <c r="J45" s="5" t="inlineStr">
         <is>
           <t>Aceptable</t>
         </is>
@@ -7805,27 +8011,32 @@
           <t>Faranda Hotels</t>
         </is>
       </c>
-      <c r="C46" s="12" t="n">
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="n">
         <v>240</v>
       </c>
-      <c r="D46" s="12" t="n">
+      <c r="E46" s="12" t="n">
         <v>237</v>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F46" s="13" t="n">
+      <c r="G46" s="13" t="n">
         <v>0.9875</v>
       </c>
-      <c r="G46" s="13" t="n">
+      <c r="H46" s="13" t="n">
         <v>0.008333333333333333</v>
       </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="I46" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="J46" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7840,27 +8051,32 @@
           <t>Dorado Plaza</t>
         </is>
       </c>
-      <c r="C47" s="12" t="n">
-        <v>217</v>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D47" s="12" t="n">
         <v>217</v>
       </c>
       <c r="E47" s="12" t="n">
+        <v>217</v>
+      </c>
+      <c r="F47" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F47" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G47" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="13" t="n">
         <v>0.009216589861751152</v>
       </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="I47" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="J47" s="5" t="inlineStr">
         <is>
           <t>Revisar</t>
         </is>
@@ -7875,27 +8091,32 @@
           <t>Krystal</t>
         </is>
       </c>
-      <c r="C48" s="12" t="n">
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
+      </c>
+      <c r="D48" s="12" t="n">
         <v>209</v>
       </c>
-      <c r="D48" s="12" t="n">
+      <c r="E48" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="13" t="n">
+      <c r="G48" s="13" t="n">
         <v>0.01435406698564593</v>
       </c>
-      <c r="G48" s="13" t="n">
+      <c r="H48" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H48" s="4" t="inlineStr">
+      <c r="I48" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I48" s="5" t="inlineStr">
+      <c r="J48" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7910,27 +8131,32 @@
           <t>BH Hoteles</t>
         </is>
       </c>
-      <c r="C49" s="12" t="n">
-        <v>187</v>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D49" s="12" t="n">
         <v>187</v>
       </c>
       <c r="E49" s="12" t="n">
+        <v>187</v>
+      </c>
+      <c r="F49" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="F49" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G49" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="13" t="n">
         <v>0.0267379679144385</v>
       </c>
-      <c r="H49" s="10" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="J49" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -7945,27 +8171,32 @@
           <t>Alsol</t>
         </is>
       </c>
-      <c r="C50" s="12" t="n">
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>Internal, Siteminder</t>
+        </is>
+      </c>
+      <c r="D50" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="D50" s="12" t="n">
+      <c r="E50" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="G50" s="13" t="n">
         <v>0.3983050847457627</v>
       </c>
-      <c r="G50" s="13" t="n">
+      <c r="H50" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H50" s="4" t="inlineStr">
+      <c r="I50" s="4" t="inlineStr">
         <is>
           <t>Súper Crítica</t>
         </is>
       </c>
-      <c r="I50" s="5" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -7980,27 +8211,32 @@
           <t>Grupo Welcome</t>
         </is>
       </c>
-      <c r="C51" s="12" t="n">
-        <v>87</v>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D51" s="12" t="n">
         <v>87</v>
       </c>
       <c r="E51" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F51" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G51" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="I51" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I51" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8015,27 +8251,32 @@
           <t>Hoteles Solar</t>
         </is>
       </c>
-      <c r="C52" s="12" t="n">
-        <v>72</v>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D52" s="12" t="n">
         <v>72</v>
       </c>
       <c r="E52" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="F52" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G52" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="I52" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I52" s="5" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8050,27 +8291,32 @@
           <t>DOT Hotels</t>
         </is>
       </c>
-      <c r="C53" s="12" t="n">
-        <v>44</v>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D53" s="12" t="n">
         <v>44</v>
       </c>
       <c r="E53" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="F53" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F53" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G53" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="13" t="n">
         <v>0.04545454545454546</v>
       </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="I53" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I53" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
@@ -8085,27 +8331,32 @@
           <t>Viaggio</t>
         </is>
       </c>
-      <c r="C54" s="12" t="n">
-        <v>42</v>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>Siteminder</t>
+        </is>
       </c>
       <c r="D54" s="12" t="n">
         <v>42</v>
       </c>
       <c r="E54" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F54" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F54" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G54" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="I54" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I54" s="5" t="inlineStr">
+      <c r="J54" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8120,27 +8371,32 @@
           <t>Lomas Hospitality</t>
         </is>
       </c>
-      <c r="C55" s="12" t="n">
-        <v>30</v>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>Internal</t>
+        </is>
       </c>
       <c r="D55" s="12" t="n">
         <v>30</v>
       </c>
       <c r="E55" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="F55" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="F55" s="13" t="n">
-        <v>1</v>
-      </c>
       <c r="G55" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="I55" s="10" t="inlineStr">
         <is>
           <t>Exitosa</t>
         </is>
       </c>
-      <c r="I55" s="5" t="inlineStr">
+      <c r="J55" s="5" t="inlineStr">
         <is>
           <t>Sin Conversión</t>
         </is>
@@ -8188,7 +8444,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10411,7 +10667,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:07 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>

--- a/checkrates/week-19/Analisis_Checkrates_B2C_7d.xlsx
+++ b/checkrates/week-19/Analisis_Checkrates_B2C_7d.xlsx
@@ -541,7 +541,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -694,7 +694,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -829,7 +829,7 @@
     <col width="24" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="43" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -854,7 +854,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
@@ -1924,7 +1924,7 @@
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="35" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
@@ -1948,7 +1948,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -4123,7 +4123,7 @@
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
@@ -4147,7 +4147,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -6320,7 +6320,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
@@ -6346,7 +6346,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -8418,7 +8418,7 @@
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
@@ -8444,7 +8444,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -8481,7 +8481,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -10262,7 +10262,7 @@
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
@@ -10288,7 +10288,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
@@ -10643,7 +10643,7 @@
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="13" customWidth="1" min="4" max="4"/>
     <col width="41" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="24" customWidth="1" min="9" max="9"/>
@@ -10667,7 +10667,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generado: 11/05/2026 22:43 · W18 · 27 abr – 3 may 2026</t>
+          <t>Generado: 12/05/2026 00:19 · W18 · 27 abr – 3 may 2026</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>CR_Unicos</t>
+          <t>Checkrates</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -10714,7 +10714,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>ConvRate</t>
+          <t>Conv Rate</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
